--- a/public/samples/Sample_Procurement_Exception_Report.xlsx
+++ b/public/samples/Sample_Procurement_Exception_Report.xlsx
@@ -495,7 +495,7 @@
         <v>Generated At</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-07-14T19:02:09.073Z</v>
+        <v>2026-07-14T21:10:05.366Z</v>
       </c>
     </row>
     <row r="14">
